--- a/Lab 10/FOTN24_Country_Score_Data.xlsx
+++ b/Lab 10/FOTN24_Country_Score_Data.xlsx
@@ -1,36 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{3A074999-4054-40F7-BB6A-D9174E99C286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4871B5F-C4EB-4F6D-BDA6-6AF92CC80B54}"/>
-  <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="FOTN 2024 score data" sheetId="1" r:id="rId1"/>
-    <sheet name="Understanding our data" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="FOTN 2024 score data" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Understanding our data" state="visible" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="115">
   <si>
+    <t>Freedom on the Net 2024 country score data</t>
+  </si>
+  <si>
     <t>Country</t>
   </si>
   <si>
@@ -157,6 +143,9 @@
     <t>Canada</t>
   </si>
   <si>
+    <t>Chile</t>
+  </si>
+  <si>
     <t>China</t>
   </si>
   <si>
@@ -295,6 +284,12 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>The Gambia</t>
+  </si>
+  <si>
+    <t>The Netherlands</t>
+  </si>
+  <si>
     <t>Tunisia</t>
   </si>
   <si>
@@ -362,77 +357,45 @@
   </si>
   <si>
     <t>Please refer to the full methodology for more details: https://freedomhouse.org/reports/freedom-net/freedom-net-research-methodology</t>
-  </si>
-  <si>
-    <t>The Gambia</t>
-  </si>
-  <si>
-    <t>Chile</t>
-  </si>
-  <si>
-    <t>The Netherlands</t>
-  </si>
-  <si>
-    <t>Freedom on the Net 2024 country score data</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
+      <sz val="13"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -442,49 +405,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBD8BD"/>
-        <bgColor rgb="FFFBD8BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8BE92"/>
-        <bgColor rgb="FFF8BE92"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9E3EF"/>
-        <bgColor rgb="FFF9E3EF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4D0E3"/>
-        <bgColor rgb="FFF4D0E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDAEAFE"/>
-        <bgColor rgb="FFDAEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB4D0FE"/>
-        <bgColor rgb="FFB4D0FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFC8E91"/>
-        <bgColor rgb="FFFC8E91"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -501,21 +451,21 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="hair">
+      <left style="dotted">
         <color rgb="FF000000"/>
       </left>
-      <right style="hair">
+      <right style="dotted">
         <color rgb="FF000000"/>
       </right>
-      <top style="hair">
+      <top style="dotted">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="hair">
+      <bottom style="dotted">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -524,51 +474,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -581,9 +527,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -621,7 +567,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -693,7 +639,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -725,20 +671,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -860,149 +802,186 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AB74"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="7.1796875" customWidth="1"/>
-    <col min="4" max="27" width="4.453125" customWidth="1"/>
-    <col min="28" max="28" width="5.81640625" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="28" width="9.285714285714286" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="2" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="1" t="s">
+    <row r="1" ht="24" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="Q2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AA2" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A3" s="13" t="s">
+      <c r="AB2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="13">
+    </row>
+    <row r="3" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="3">
         <v>2024</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>29</v>
+      <c r="C3" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D3" s="4">
         <v>2</v>
@@ -1080,15 +1059,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A4" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="13">
+    <row r="4" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="3">
         <v>2024</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>31</v>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D4" s="4">
         <v>5</v>
@@ -1166,15 +1145,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A5" s="13" t="s">
+    <row r="5" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B5" s="13">
-        <v>2024</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>31</v>
       </c>
       <c r="D5" s="4">
         <v>5</v>
@@ -1252,15 +1231,15 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="13">
+    <row r="6" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="3">
         <v>2024</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>31</v>
+      <c r="C6" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D6" s="4">
         <v>6</v>
@@ -1338,15 +1317,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A7" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="13">
+    <row r="7" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="3">
         <v>2024</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>35</v>
+      <c r="C7" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D7" s="4">
         <v>5</v>
@@ -1424,15 +1403,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A8" s="13" t="s">
+    <row r="8" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="B8" s="13">
-        <v>2024</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>35</v>
       </c>
       <c r="D8" s="4">
         <v>6</v>
@@ -1510,15 +1489,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A9" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="13">
+    <row r="9" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="3">
         <v>2024</v>
       </c>
-      <c r="C9" s="14" t="s">
-        <v>29</v>
+      <c r="C9" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D9" s="4">
         <v>3</v>
@@ -1596,15 +1575,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="13">
+    <row r="10" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="3">
         <v>2024</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>35</v>
+      <c r="C10" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D10" s="4">
         <v>5</v>
@@ -1682,15 +1661,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A11" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="13">
+    <row r="11" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3">
         <v>2024</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>29</v>
+      <c r="C11" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D11" s="4">
         <v>5</v>
@@ -1768,15 +1747,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A12" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="13">
+    <row r="12" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="3">
         <v>2024</v>
       </c>
-      <c r="C12" s="14" t="s">
-        <v>29</v>
+      <c r="C12" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D12" s="4">
         <v>4</v>
@@ -1854,15 +1833,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="13">
+    <row r="13" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="3">
         <v>2024</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>31</v>
+      <c r="C13" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D13" s="4">
         <v>6</v>
@@ -1940,15 +1919,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A14" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="13">
+    <row r="14" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3">
         <v>2024</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>31</v>
+      <c r="C14" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D14" s="4">
         <v>6</v>
@@ -2026,15 +2005,15 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A15" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="13">
+    <row r="15" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="3">
         <v>2024</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>35</v>
+      <c r="C15" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D15" s="4">
         <v>5</v>
@@ -2112,15 +2091,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A16" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="13">
+    <row r="16" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="3">
         <v>2024</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>29</v>
+      <c r="C16" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D16" s="4">
         <v>5</v>
@@ -2198,15 +2177,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="17" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A17" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="13">
+    <row r="17" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="3">
         <v>2024</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>31</v>
+      <c r="C17" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D17" s="4">
         <v>5</v>
@@ -2284,15 +2263,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="13">
+    <row r="18" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="3">
         <v>2024</v>
       </c>
-      <c r="C18" s="14" t="s">
-        <v>35</v>
+      <c r="C18" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D18" s="4">
         <v>2</v>
@@ -2370,15 +2349,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A19" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="13">
+    <row r="19" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="3">
         <v>2024</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>29</v>
+      <c r="C19" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D19" s="4">
         <v>5</v>
@@ -2456,15 +2435,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A20" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="13">
+    <row r="20" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="3">
         <v>2024</v>
       </c>
-      <c r="C20" s="14" t="s">
-        <v>35</v>
+      <c r="C20" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D20" s="4">
         <v>4</v>
@@ -2542,15 +2521,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A21" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="13">
+    <row r="21" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="3">
         <v>2024</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>31</v>
+      <c r="C21" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D21" s="4">
         <v>6</v>
@@ -2628,15 +2607,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A22" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B22" s="13">
+    <row r="22" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="3">
         <v>2024</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>35</v>
+      <c r="C22" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
@@ -2714,15 +2693,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A23" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="13">
+    <row r="23" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="3">
         <v>2024</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>31</v>
+      <c r="C23" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D23" s="4">
         <v>6</v>
@@ -2800,15 +2779,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A24" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="13">
+    <row r="24" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="3">
         <v>2024</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>31</v>
+      <c r="C24" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D24" s="4">
         <v>5</v>
@@ -2886,15 +2865,15 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A25" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="13">
+    <row r="25" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="3">
         <v>2024</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>31</v>
+      <c r="C25" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D25" s="4">
         <v>6</v>
@@ -2972,15 +2951,15 @@
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A26" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="13">
+    <row r="26" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="3">
         <v>2024</v>
       </c>
-      <c r="C26" s="14" t="s">
-        <v>29</v>
+      <c r="C26" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D26" s="4">
         <v>3</v>
@@ -3058,15 +3037,15 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A27" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="13">
+    <row r="27" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="3">
         <v>2024</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>29</v>
+      <c r="C27" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D27" s="4">
         <v>6</v>
@@ -3144,15 +3123,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="28" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A28" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" s="13">
+    <row r="28" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="3">
         <v>2024</v>
       </c>
-      <c r="C28" s="14" t="s">
-        <v>31</v>
+      <c r="C28" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D28" s="4">
         <v>6</v>
@@ -3230,15 +3209,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A29" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="13">
+    <row r="29" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3">
         <v>2024</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>29</v>
+      <c r="C29" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D29" s="4">
         <v>4</v>
@@ -3316,15 +3295,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A30" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="13">
+    <row r="30" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="3">
         <v>2024</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>29</v>
+      <c r="C30" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D30" s="4">
         <v>4</v>
@@ -3402,15 +3381,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A31" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="B31" s="13">
+    <row r="31" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="3">
         <v>2024</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>35</v>
+      <c r="C31" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D31" s="4">
         <v>5</v>
@@ -3488,15 +3467,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A32" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="13">
+    <row r="32" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="3">
         <v>2024</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>29</v>
+      <c r="C32" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D32" s="4">
         <v>3</v>
@@ -3574,15 +3553,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A33" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="13">
+    <row r="33" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" s="3">
         <v>2024</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>31</v>
+      <c r="C33" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D33" s="4">
         <v>5</v>
@@ -3660,15 +3639,15 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A34" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" s="13">
+    <row r="34" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="3">
         <v>2024</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>31</v>
+      <c r="C34" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D34" s="4">
         <v>6</v>
@@ -3746,15 +3725,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A35" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="13">
+    <row r="35" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="3">
         <v>2024</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>29</v>
+      <c r="C35" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D35" s="4">
         <v>5</v>
@@ -3832,15 +3811,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A36" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="13">
+    <row r="36" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="3">
         <v>2024</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>35</v>
+      <c r="C36" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D36" s="4">
         <v>5</v>
@@ -3918,15 +3897,15 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A37" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B37" s="13">
+    <row r="37" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="3">
         <v>2024</v>
       </c>
-      <c r="C37" s="14" t="s">
-        <v>29</v>
+      <c r="C37" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D37" s="4">
         <v>3</v>
@@ -4004,15 +3983,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A38" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="13">
+    <row r="38" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B38" s="3">
         <v>2024</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>29</v>
+      <c r="C38" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D38" s="4">
         <v>5</v>
@@ -4090,15 +4069,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A39" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="13">
+    <row r="39" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B39" s="3">
         <v>2024</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>29</v>
+      <c r="C39" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D39" s="4">
         <v>3</v>
@@ -4176,15 +4155,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A40" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B40" s="13">
+    <row r="40" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="3">
         <v>2024</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>29</v>
+      <c r="C40" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D40" s="4">
         <v>3</v>
@@ -4262,15 +4241,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A41" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B41" s="13">
+    <row r="41" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B41" s="3">
         <v>2024</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>29</v>
+      <c r="C41" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D41" s="4">
         <v>1</v>
@@ -4348,15 +4327,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A42" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B42" s="13">
+    <row r="42" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="3">
         <v>2024</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>29</v>
+      <c r="C42" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D42" s="4">
         <v>6</v>
@@ -4434,15 +4413,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="43" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A43" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B43" s="13">
+    <row r="43" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" s="3">
         <v>2024</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>29</v>
+      <c r="C43" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D43" s="4">
         <v>5</v>
@@ -4520,15 +4499,15 @@
         <v>61</v>
       </c>
     </row>
-    <row r="44" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A44" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B44" s="13">
+    <row r="44" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="3">
         <v>2024</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>29</v>
+      <c r="C44" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D44" s="4">
         <v>5</v>
@@ -4606,15 +4585,15 @@
         <v>54</v>
       </c>
     </row>
-    <row r="45" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A45" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B45" s="13">
+    <row r="45" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B45" s="3">
         <v>2024</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>35</v>
+      <c r="C45" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D45" s="4">
         <v>2</v>
@@ -4692,15 +4671,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A46" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B46" s="13">
+    <row r="46" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="3">
         <v>2024</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>29</v>
+      <c r="C46" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D46" s="4">
         <v>3</v>
@@ -4778,15 +4757,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="47" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A47" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B47" s="13">
+    <row r="47" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B47" s="3">
         <v>2024</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>29</v>
+      <c r="C47" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D47" s="4">
         <v>3</v>
@@ -4864,15 +4843,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A48" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="13">
+    <row r="48" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B48" s="3">
         <v>2024</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>35</v>
+      <c r="C48" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D48" s="4">
         <v>2</v>
@@ -4950,15 +4929,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="49" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A49" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B49" s="13">
+    <row r="49" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B49" s="3">
         <v>2024</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>29</v>
+      <c r="C49" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D49" s="4">
         <v>4</v>
@@ -5036,15 +5015,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="50" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A50" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B50" s="13">
+    <row r="50" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="3">
         <v>2024</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>35</v>
+      <c r="C50" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D50" s="4">
         <v>5</v>
@@ -5122,15 +5101,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A51" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B51" s="13">
+    <row r="51" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B51" s="3">
         <v>2024</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>35</v>
+      <c r="C51" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D51" s="4">
         <v>3</v>
@@ -5208,15 +5187,15 @@
         <v>36</v>
       </c>
     </row>
-    <row r="52" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A52" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B52" s="13">
+    <row r="52" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" s="3">
         <v>2024</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>35</v>
+      <c r="C52" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D52" s="4">
         <v>6</v>
@@ -5294,15 +5273,15 @@
         <v>25</v>
       </c>
     </row>
-    <row r="53" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A53" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="13">
+    <row r="53" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" s="3">
         <v>2024</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>31</v>
+      <c r="C53" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D53" s="4">
         <v>6</v>
@@ -5380,15 +5359,15 @@
         <v>70</v>
       </c>
     </row>
-    <row r="54" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A54" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B54" s="13">
+    <row r="54" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="3">
         <v>2024</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>29</v>
+      <c r="C54" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D54" s="4">
         <v>6</v>
@@ -5466,15 +5445,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="55" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A55" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B55" s="13">
+    <row r="55" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="3">
         <v>2024</v>
       </c>
-      <c r="C55" s="14" t="s">
-        <v>31</v>
+      <c r="C55" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D55" s="4">
         <v>5</v>
@@ -5552,15 +5531,15 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A56" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B56" s="13">
+    <row r="56" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="3">
         <v>2024</v>
       </c>
-      <c r="C56" s="14" t="s">
-        <v>29</v>
+      <c r="C56" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D56" s="4">
         <v>6</v>
@@ -5638,15 +5617,15 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A57" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B57" s="13">
+    <row r="57" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B57" s="3">
         <v>2024</v>
       </c>
-      <c r="C57" s="14" t="s">
-        <v>29</v>
+      <c r="C57" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D57" s="4">
         <v>4</v>
@@ -5724,15 +5703,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A58" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B58" s="13">
+    <row r="58" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="3">
         <v>2024</v>
       </c>
-      <c r="C58" s="14" t="s">
-        <v>35</v>
+      <c r="C58" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D58" s="4">
         <v>1</v>
@@ -5810,15 +5789,15 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A59" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B59" s="13">
+    <row r="59" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B59" s="3">
         <v>2024</v>
       </c>
-      <c r="C59" s="14" t="s">
-        <v>31</v>
+      <c r="C59" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D59" s="4">
         <v>6</v>
@@ -5896,15 +5875,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="60" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A60" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B60" s="13">
+    <row r="60" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="3">
         <v>2024</v>
       </c>
-      <c r="C60" s="14" t="s">
-        <v>35</v>
+      <c r="C60" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D60" s="4">
         <v>5</v>
@@ -5982,15 +5961,15 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A61" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="B61" s="13">
+    <row r="61" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B61" s="3">
         <v>2024</v>
       </c>
-      <c r="C61" s="14" t="s">
-        <v>29</v>
+      <c r="C61" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D61" s="4">
         <v>2</v>
@@ -6068,15 +6047,15 @@
         <v>56</v>
       </c>
     </row>
-    <row r="62" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A62" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B62" s="13">
+    <row r="62" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B62" s="3">
         <v>2024</v>
       </c>
-      <c r="C62" s="14" t="s">
-        <v>31</v>
+      <c r="C62" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D62" s="4">
         <v>6</v>
@@ -6154,15 +6133,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A63" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B63" s="13">
+    <row r="63" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="3">
         <v>2024</v>
       </c>
-      <c r="C63" s="14" t="s">
-        <v>29</v>
+      <c r="C63" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D63" s="4">
         <v>4</v>
@@ -6240,15 +6219,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="64" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A64" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B64" s="13">
+    <row r="64" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="3">
         <v>2024</v>
       </c>
-      <c r="C64" s="14" t="s">
-        <v>35</v>
+      <c r="C64" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D64" s="4">
         <v>5</v>
@@ -6326,15 +6305,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A65" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B65" s="13">
+    <row r="65" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B65" s="3">
         <v>2024</v>
       </c>
-      <c r="C65" s="14" t="s">
-        <v>29</v>
+      <c r="C65" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D65" s="4">
         <v>2</v>
@@ -6412,15 +6391,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="66" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A66" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="B66" s="13">
+    <row r="66" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B66" s="3">
         <v>2024</v>
       </c>
-      <c r="C66" s="14" t="s">
-        <v>29</v>
+      <c r="C66" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D66" s="4">
         <v>4</v>
@@ -6498,15 +6477,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A67" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="B67" s="13">
+    <row r="67" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" s="3">
         <v>2024</v>
       </c>
-      <c r="C67" s="14" t="s">
-        <v>35</v>
+      <c r="C67" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D67" s="4">
         <v>6</v>
@@ -6584,15 +6563,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A68" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B68" s="13">
+    <row r="68" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B68" s="3">
         <v>2024</v>
       </c>
-      <c r="C68" s="14" t="s">
-        <v>31</v>
+      <c r="C68" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D68" s="4">
         <v>6</v>
@@ -6670,15 +6649,15 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A69" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="13">
+    <row r="69" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B69" s="3">
         <v>2024</v>
       </c>
-      <c r="C69" s="14" t="s">
-        <v>31</v>
+      <c r="C69" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="D69" s="4">
         <v>6</v>
@@ -6756,15 +6735,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A70" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B70" s="13">
+    <row r="70" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B70" s="3">
         <v>2024</v>
       </c>
-      <c r="C70" s="14" t="s">
-        <v>35</v>
+      <c r="C70" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D70" s="4">
         <v>5</v>
@@ -6842,15 +6821,15 @@
         <v>27</v>
       </c>
     </row>
-    <row r="71" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A71" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B71" s="13">
+    <row r="71" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="3">
         <v>2024</v>
       </c>
-      <c r="C71" s="14" t="s">
-        <v>35</v>
+      <c r="C71" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D71" s="4">
         <v>3</v>
@@ -6928,15 +6907,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="72" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A72" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B72" s="13">
+    <row r="72" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B72" s="3">
         <v>2024</v>
       </c>
-      <c r="C72" s="14" t="s">
-        <v>35</v>
+      <c r="C72" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D72" s="4">
         <v>4</v>
@@ -7014,15 +6993,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A73" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B73" s="13">
+    <row r="73" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" s="3">
         <v>2024</v>
       </c>
-      <c r="C73" s="14" t="s">
-        <v>29</v>
+      <c r="C73" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D73" s="4">
         <v>2</v>
@@ -7100,15 +7079,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="74" spans="1:28" ht="17" x14ac:dyDescent="0.4">
-      <c r="A74" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B74" s="13">
+    <row r="74" ht="17.25" customHeight="1" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" s="3">
         <v>2024</v>
       </c>
-      <c r="C74" s="14" t="s">
-        <v>29</v>
+      <c r="C74" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D74" s="4">
         <v>1</v>
@@ -7191,386 +7170,78 @@
     <mergeCell ref="A1:AB1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="137.71428571428572" customWidth="1"/>
+    <col min="2" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="K6" s="12"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K7" s="12"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+      <c r="K7" s="13"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EDAE4BACD1F4F449AF1E45E0F4042A8E" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0c4ecdd66df0c8316e872b37932ffeb2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aedc87c9-fa16-4ea4-92d3-41d4e2157c0b" xmlns:ns3="3d854844-489d-4a5d-b4ab-ea994fd25330" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7e8b269513d1748eeb8b30f491f404cd" ns2:_="" ns3:_="">
-    <xsd:import namespace="aedc87c9-fa16-4ea4-92d3-41d4e2157c0b"/>
-    <xsd:import namespace="3d854844-489d-4a5d-b4ab-ea994fd25330"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aedc87c9-fa16-4ea4-92d3-41d4e2157c0b" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="18" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2394a132-982a-4dbf-8bea-cf3d3a72dbf7" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3d854844-489d-4a5d-b4ab-ea994fd25330" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{67f0c8c4-ee44-4ead-9d67-108c9de97923}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3d854844-489d-4a5d-b4ab-ea994fd25330">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3d854844-489d-4a5d-b4ab-ea994fd25330" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aedc87c9-fa16-4ea4-92d3-41d4e2157c0b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9ED438C-9385-4A5F-8087-9CFFB3372B97}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="aedc87c9-fa16-4ea4-92d3-41d4e2157c0b"/>
-    <ds:schemaRef ds:uri="3d854844-489d-4a5d-b4ab-ea994fd25330"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{218AC18F-BD12-467A-ACFE-565F5655DB48}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3d854844-489d-4a5d-b4ab-ea994fd25330"/>
-    <ds:schemaRef ds:uri="aedc87c9-fa16-4ea4-92d3-41d4e2157c0b"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07BE9147-6FE2-4110-A3E0-B74171FC4D92}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>